--- a/Liste_Bewirtung.xlsx
+++ b/Liste_Bewirtung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff38c7f2fb15de3e/04_Privat/TCM/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{2FFFAFA0-CF7F-423B-945C-B77AA0945887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A180B915-08FE-45B6-86AD-95F515DDE6AA}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="8_{2FFFAFA0-CF7F-423B-945C-B77AA0945887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68A702AB-A9ED-4A3E-87D6-E0542673839B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87B39E5F-0CDE-4DFD-A517-00E6B6C8911A}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87B39E5F-0CDE-4DFD-A517-00E6B6C8911A}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="81">
   <si>
     <t>30.4.</t>
   </si>
@@ -255,6 +255,30 @@
   </si>
   <si>
     <t>Wurst/Steak</t>
+  </si>
+  <si>
+    <t>Anna B.</t>
+  </si>
+  <si>
+    <t>Savannah S.</t>
+  </si>
+  <si>
+    <t>Jule V.</t>
+  </si>
+  <si>
+    <t>Tabea H.</t>
+  </si>
+  <si>
+    <t>Jutta M.</t>
+  </si>
+  <si>
+    <t>Mara M.</t>
+  </si>
+  <si>
+    <t>Sandra M.</t>
+  </si>
+  <si>
+    <t>Amy M.</t>
   </si>
 </sst>
 </file>
@@ -307,6 +331,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -764,10 +792,10 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
         <v>66</v>
@@ -806,10 +834,10 @@
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
         <v>66</v>
@@ -862,10 +890,10 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
         <v>66</v>
@@ -1033,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
         <v>66</v>

--- a/Liste_Bewirtung.xlsx
+++ b/Liste_Bewirtung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff38c7f2fb15de3e/04_Privat/TCM/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="8_{2FFFAFA0-CF7F-423B-945C-B77AA0945887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68A702AB-A9ED-4A3E-87D6-E0542673839B}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="8_{2FFFAFA0-CF7F-423B-945C-B77AA0945887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F334BD15-39D4-459F-BA81-39138FF8A94F}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87B39E5F-0CDE-4DFD-A517-00E6B6C8911A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="82">
   <si>
     <t>30.4.</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>Amy M.</t>
+  </si>
+  <si>
+    <t>Penne all' Arrabbiata, schöne Salate, Wienerle und Debreziner, verschiedene Leckerein, Käse</t>
   </si>
 </sst>
 </file>
@@ -744,6 +747,9 @@
       <c r="D6" t="s">
         <v>66</v>
       </c>
+      <c r="E6" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
